--- a/fhir/ig/r2bo/0.3.0-draft/StructureDefinition-ModeloLogicoPacienteR2BO.xlsx
+++ b/fhir/ig/r2bo/0.3.0-draft/StructureDefinition-ModeloLogicoPacienteR2BO.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:25:24-04:00</t>
+    <t>2026-08-20T16:22:48-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
